--- a/assignments/제출용/식용작물학1_감자_분석.xlsx
+++ b/assignments/제출용/식용작물학1_감자_분석.xlsx
@@ -60,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -82,11 +82,55 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -108,6 +152,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -28432,10 +28482,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -28453,6 +28503,9 @@
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28575,6 +28628,24 @@
 감자 면적(ha)</t>
         </is>
       </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>[참고] 일반봄감자 면적
+전년 대비(%)</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>[참고] 고랭지감자 면적
+전년 대비(%)</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>[참고] 가을감자 면적
+전년 대비(%)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -28647,6 +28718,21 @@
         <f>'Raw data'!H21</f>
         <v>6174</v>
       </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -28716,6 +28802,18 @@
         <f>'Raw data'!Y21</f>
         <v>4167</v>
       </c>
+      <c r="S6" s="6">
+        <f>IF(OR(L6="",L5=""),"",(L6-L5)/L5*100)</f>
+        <v>-25.3306713251809</v>
+      </c>
+      <c r="T6" s="6">
+        <f>IF(OR(M6="",M5=""),"",(M6-M5)/M5*100)</f>
+        <v>-9.44127708095781</v>
+      </c>
+      <c r="U6" s="6">
+        <f>IF(OR(N6="",N5=""),"",(N6-N5)/N5*100)</f>
+        <v>-39.5040924410207</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -28785,6 +28883,18 @@
         <f>'Raw data'!AP21</f>
         <v>2717</v>
       </c>
+      <c r="S7" s="6">
+        <f>IF(OR(L7="",L6=""),"",(L7-L6)/L6*100)</f>
+        <v>-12.8810160427807</v>
+      </c>
+      <c r="T7" s="6">
+        <f>IF(OR(M7="",M6=""),"",(M7-M6)/M6*100)</f>
+        <v>-19.3653991437925</v>
+      </c>
+      <c r="U7" s="6">
+        <f>IF(OR(N7="",N6=""),"",(N7-N6)/N6*100)</f>
+        <v>-16.7130919220056</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -28854,6 +28964,18 @@
         <f>'Raw data'!BG21</f>
         <v>2663</v>
       </c>
+      <c r="S8" s="6">
+        <f>IF(OR(L8="",L7=""),"",(L8-L7)/L7*100)</f>
+        <v>0.115092457607611</v>
+      </c>
+      <c r="T8" s="6">
+        <f>IF(OR(M8="",M7=""),"",(M8-M7)/M7*100)</f>
+        <v>5.05933791380387</v>
+      </c>
+      <c r="U8" s="6">
+        <f>IF(OR(N8="",N7=""),"",(N8-N7)/N7*100)</f>
+        <v>-1.38557095078834</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -28923,6 +29045,18 @@
         <f>'Raw data'!BX21</f>
         <v>2413</v>
       </c>
+      <c r="S9" s="6">
+        <f>IF(OR(L9="",L8=""),"",(L9-L8)/L8*100)</f>
+        <v>8.81361128142244</v>
+      </c>
+      <c r="T9" s="6">
+        <f>IF(OR(M9="",M8=""),"",(M9-M8)/M8*100)</f>
+        <v>-1.24851367419738</v>
+      </c>
+      <c r="U9" s="6">
+        <f>IF(OR(N9="",N8=""),"",(N9-N8)/N8*100)</f>
+        <v>-6.1046511627907</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -28992,6 +29126,18 @@
         <f>'Raw data'!CO21</f>
         <v>2766</v>
       </c>
+      <c r="S10" s="6">
+        <f>IF(OR(L10="",L9=""),"",(L10-L9)/L9*100)</f>
+        <v>14.8189885899422</v>
+      </c>
+      <c r="T10" s="6">
+        <f>IF(OR(M10="",M9=""),"",(M10-M9)/M9*100)</f>
+        <v>14.4190246839253</v>
+      </c>
+      <c r="U10" s="6">
+        <f>IF(OR(N10="",N9=""),"",(N10-N9)/N9*100)</f>
+        <v>24.0970072239422</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -29061,6 +29207,18 @@
         <f>'Raw data'!DF21</f>
         <v>2814</v>
       </c>
+      <c r="S11" s="6">
+        <f>IF(OR(L11="",L10=""),"",(L11-L10)/L10*100)</f>
+        <v>17.3230278493436</v>
+      </c>
+      <c r="T11" s="6">
+        <f>IF(OR(M11="",M10=""),"",(M11-M10)/M10*100)</f>
+        <v>-0.447250723493817</v>
+      </c>
+      <c r="U11" s="6">
+        <f>IF(OR(N11="",N10=""),"",(N11-N10)/N10*100)</f>
+        <v>-19.043659043659</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -29130,6 +29288,18 @@
         <f>'Raw data'!DW21</f>
         <v>2574</v>
       </c>
+      <c r="S12" s="6">
+        <f>IF(OR(L12="",L11=""),"",(L12-L11)/L11*100)</f>
+        <v>-8.89888110425599</v>
+      </c>
+      <c r="T12" s="6">
+        <f>IF(OR(M12="",M11=""),"",(M12-M11)/M11*100)</f>
+        <v>0.23784355179704</v>
+      </c>
+      <c r="U12" s="6">
+        <f>IF(OR(N12="",N11=""),"",(N12-N11)/N11*100)</f>
+        <v>-4.64817668207499</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -29199,6 +29369,18 @@
         <f>'Raw data'!EN21</f>
         <v>1797</v>
       </c>
+      <c r="S13" s="6">
+        <f>IF(OR(L13="",L12=""),"",(L13-L12)/L12*100)</f>
+        <v>20.3914141414141</v>
+      </c>
+      <c r="T13" s="6">
+        <f>IF(OR(M13="",M12=""),"",(M13-M12)/M12*100)</f>
+        <v>-1.10730292644345</v>
+      </c>
+      <c r="U13" s="6">
+        <f>IF(OR(N13="",N12=""),"",(N13-N12)/N12*100)</f>
+        <v>-27.2286560732561</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -29268,6 +29450,18 @@
         <f>'Raw data'!FE21</f>
         <v>1382</v>
       </c>
+      <c r="S14" s="6">
+        <f>IF(OR(L14="",L13=""),"",(L14-L13)/L13*100)</f>
+        <v>-25.651904466797</v>
+      </c>
+      <c r="T14" s="6">
+        <f>IF(OR(M14="",M13=""),"",(M14-M13)/M13*100)</f>
+        <v>-20.6878165822447</v>
+      </c>
+      <c r="U14" s="6">
+        <f>IF(OR(N14="",N13=""),"",(N14-N13)/N13*100)</f>
+        <v>7.36491487786825</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -29337,6 +29531,18 @@
         <f>'Raw data'!FV21</f>
         <v>1129</v>
       </c>
+      <c r="S15" s="6">
+        <f>IF(OR(L15="",L14=""),"",(L15-L14)/L14*100)</f>
+        <v>-6.73890741215696</v>
+      </c>
+      <c r="T15" s="6">
+        <f>IF(OR(M15="",M14=""),"",(M15-M14)/M14*100)</f>
+        <v>14.3865546218487</v>
+      </c>
+      <c r="U15" s="6">
+        <f>IF(OR(N15="",N14=""),"",(N15-N14)/N14*100)</f>
+        <v>-21.1995863495346</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -29406,6 +29612,18 @@
         <f>'Raw data'!GM21</f>
         <v>1781</v>
       </c>
+      <c r="S16" s="6">
+        <f>IF(OR(L16="",L15=""),"",(L16-L15)/L15*100)</f>
+        <v>4.90890340323135</v>
+      </c>
+      <c r="T16" s="6">
+        <f>IF(OR(M16="",M15=""),"",(M16-M15)/M15*100)</f>
+        <v>5.17190714075815</v>
+      </c>
+      <c r="U16" s="6">
+        <f>IF(OR(N16="",N15=""),"",(N16-N15)/N15*100)</f>
+        <v>38.3202099737533</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -29475,6 +29693,18 @@
         <f>'Raw data'!HD21</f>
         <v>1571</v>
       </c>
+      <c r="S17" s="6">
+        <f>IF(OR(L17="",L16=""),"",(L17-L16)/L16*100)</f>
+        <v>-2.07090897175437</v>
+      </c>
+      <c r="T17" s="6">
+        <f>IF(OR(M17="",M16=""),"",(M17-M16)/M16*100)</f>
+        <v>-9.36015646828723</v>
+      </c>
+      <c r="U17" s="6">
+        <f>IF(OR(N17="",N16=""),"",(N17-N16)/N16*100)</f>
+        <v>-11.8595825426945</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -29544,6 +29774,18 @@
         <f>'Raw data'!HU21</f>
         <v>2104</v>
       </c>
+      <c r="S18" s="6">
+        <f>IF(OR(L18="",L17=""),"",(L18-L17)/L17*100)</f>
+        <v>5.86227665127484</v>
+      </c>
+      <c r="T18" s="6">
+        <f>IF(OR(M18="",M17=""),"",(M18-M17)/M17*100)</f>
+        <v>6.72009864364981</v>
+      </c>
+      <c r="U18" s="6">
+        <f>IF(OR(N18="",N17=""),"",(N18-N17)/N17*100)</f>
+        <v>47.865087908145</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -29613,6 +29855,18 @@
         <f>'Raw data'!IL21</f>
         <v>1653</v>
       </c>
+      <c r="S19" s="6">
+        <f>IF(OR(L19="",L18=""),"",(L19-L18)/L18*100)</f>
+        <v>14.7354447183766</v>
+      </c>
+      <c r="T19" s="6">
+        <f>IF(OR(M19="",M18=""),"",(M19-M18)/M18*100)</f>
+        <v>11.0340843443096</v>
+      </c>
+      <c r="U19" s="6">
+        <f>IF(OR(N19="",N18=""),"",(N19-N18)/N18*100)</f>
+        <v>17.3258917738413</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -29682,6 +29936,18 @@
         <f>'Raw data'!JC21</f>
         <v>1565</v>
       </c>
+      <c r="S20" s="6">
+        <f>IF(OR(L20="",L19=""),"",(L20-L19)/L19*100)</f>
+        <v>-9.97796143250689</v>
+      </c>
+      <c r="T20" s="6">
+        <f>IF(OR(M20="",M19=""),"",(M20-M19)/M19*100)</f>
+        <v>-11.8106139438085</v>
+      </c>
+      <c r="U20" s="6">
+        <f>IF(OR(N20="",N19=""),"",(N20-N19)/N19*100)</f>
+        <v>-19.9586349534643</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -29751,6 +30017,18 @@
         <f>'Raw data'!JT21</f>
         <v>1732</v>
       </c>
+      <c r="S21" s="6">
+        <f>IF(OR(L21="",L20=""),"",(L21-L20)/L20*100)</f>
+        <v>-12.6874349715405</v>
+      </c>
+      <c r="T21" s="6">
+        <f>IF(OR(M21="",M20=""),"",(M21-M20)/M20*100)</f>
+        <v>14.6902654867257</v>
+      </c>
+      <c r="U21" s="6">
+        <f>IF(OR(N21="",N20=""),"",(N21-N20)/N20*100)</f>
+        <v>-7.2093023255814</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -29820,6 +30098,18 @@
         <f>'Raw data'!KK21</f>
         <v>1759</v>
       </c>
+      <c r="S22" s="6">
+        <f>IF(OR(L22="",L21=""),"",(L22-L21)/L21*100)</f>
+        <v>-8.75508201317819</v>
+      </c>
+      <c r="T22" s="6">
+        <f>IF(OR(M22="",M21=""),"",(M22-M21)/M21*100)</f>
+        <v>-10.108024691358</v>
+      </c>
+      <c r="U22" s="6">
+        <f>IF(OR(N22="",N21=""),"",(N22-N21)/N21*100)</f>
+        <v>-0.417710944026734</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -29889,6 +30179,18 @@
         <f>'Raw data'!LB21</f>
         <v>1238</v>
       </c>
+      <c r="S23" s="6">
+        <f>IF(OR(L23="",L22=""),"",(L23-L22)/L22*100)</f>
+        <v>12.9215641084735</v>
+      </c>
+      <c r="T23" s="6">
+        <f>IF(OR(M23="",M22=""),"",(M23-M22)/M22*100)</f>
+        <v>9.72818311874106</v>
+      </c>
+      <c r="U23" s="6">
+        <f>IF(OR(N23="",N22=""),"",(N23-N22)/N22*100)</f>
+        <v>11.6331096196868</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -29958,6 +30260,18 @@
         <f>'Raw data'!LS21</f>
         <v>1803</v>
       </c>
+      <c r="S24" s="6">
+        <f>IF(OR(L24="",L23=""),"",(L24-L23)/L23*100)</f>
+        <v>5.59221715762977</v>
+      </c>
+      <c r="T24" s="6">
+        <f>IF(OR(M24="",M23=""),"",(M24-M23)/M23*100)</f>
+        <v>2.42503259452412</v>
+      </c>
+      <c r="U24" s="6">
+        <f>IF(OR(N24="",N23=""),"",(N24-N23)/N23*100)</f>
+        <v>13.2264529058116</v>
+      </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -29984,7 +30298,376 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>보고서 결과해석에 인용한 추가 계산 (모두 수식)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>해당 연도</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>계산 방법</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>재배면적 최소값(ha)</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="5">
+        <f>MIN($B$5:$B$24)</f>
+        <v>20088</v>
+      </c>
+      <c r="F30" s="4">
+        <f>INDEX($A$5:$A$24,MATCH(E30,$B$5:$B$24,0))</f>
+        <v>2022</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>MIN(재배면적), 연도는 INDEX·MATCH</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>단수 최대값(kg/10a)</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="5">
+        <f>MAX($C$5:$C$24)</f>
+        <v>2943</v>
+      </c>
+      <c r="F31" s="4">
+        <f>INDEX($A$5:$A$24,MATCH(E31,$C$5:$C$24,0))</f>
+        <v>2008</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>MAX(단수)</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>총생산량 최소값(톤)</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="5">
+        <f>MIN($D$5:$D$24)</f>
+        <v>466755</v>
+      </c>
+      <c r="F32" s="4">
+        <f>INDEX($A$5:$A$24,MATCH(E32,$D$5:$D$24,0))</f>
+        <v>2017</v>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>MIN(총생산량)</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>일반봄감자 단수 최소값(kg/10a)</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="5">
+        <f>MIN($O$5:$O$24)</f>
+        <v>2152</v>
+      </c>
+      <c r="F33" s="4">
+        <f>INDEX($A$5:$A$24,MATCH(E33,$O$5:$O$24,0))</f>
+        <v>2017</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>MIN(일반봄감자 단수, O열)</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>전국 재배면적 감소량(ha)</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="5">
+        <f>B5-INDEX($B$5:$B$24,COUNT($D$5:$D$24))</f>
+        <v>8759</v>
+      </c>
+      <c r="F34" s="4" t="str">
+        <f>A5&amp;"→"&amp;INDEX($A$5:$A$24,COUNT($D$5:$D$24))</f>
+        <v>2005→2024</v>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>시작연도 값 − 최종연도 값</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>제주 재배면적 감소량(ha)</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="5">
+        <f>R5-INDEX($R$5:$R$24,COUNT($D$5:$D$24))</f>
+        <v>4371</v>
+      </c>
+      <c r="F35" s="4" t="str">
+        <f>A5&amp;"→"&amp;INDEX($A$5:$A$24,COUNT($D$5:$D$24))</f>
+        <v>2005→2024</v>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>시작연도 값 − 최종연도 값 (R열, 제주)</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>제주 감소량 ÷ 전국 감소량(%)</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="6">
+        <f>E35/E34*100</f>
+        <v>49.9029569585569</v>
+      </c>
+      <c r="F36" s="4" t="str">
+        <f>A5&amp;"→"&amp;INDEX($A$5:$A$24,COUNT($D$5:$D$24))</f>
+        <v>2005→2024</v>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>제주 감소량 ÷ 전국 감소량 × 100</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>최종연도 면적으로 시작연도 생산량을 내는 데 필요한 단수(kg/10a)</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="5">
+        <f>D5/INDEX($B$5:$B$24,COUNT($D$5:$D$24))*100</f>
+        <v>3730.71467311945</v>
+      </c>
+      <c r="F37" s="4" t="str">
+        <f>A5&amp;"→"&amp;INDEX($A$5:$A$24,COUNT($D$5:$D$24))</f>
+        <v>2005→2024</v>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>시작연도 생산량(톤)×1000 ÷ (최종연도 면적(ha)×10)</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>필요 단수가 단수 최대값보다 높은 비율(%)</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="6">
+        <f>(E37/E31-1)*100</f>
+        <v>26.7657041494885</v>
+      </c>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>(필요 단수 ÷ 단수 최대값 − 1) × 100</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>일반봄감자 재배면적 전년 대비 변화율(%)</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="6">
+        <f>INDEX($S$5:$S$24,MATCH(F39,$A$5:$A$24,0))</f>
+        <v>-25.3306713251809</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>2006</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>S열(전년 대비 변화율)에서 해당 연도 값</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>가을감자 재배면적 전년 대비 변화율(%)</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="6">
+        <f>INDEX($U$5:$U$24,MATCH(F40,$A$5:$A$24,0))</f>
+        <v>-39.5040924410207</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>2006</v>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>U열(전년 대비 변화율)에서 해당 연도 값</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="n"/>
+      <c r="I40" s="12" t="n"/>
+      <c r="J40" s="12" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>가을감자 재배면적 전년 대비 변화율(%)</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="6">
+        <f>INDEX($U$5:$U$24,MATCH(F41,$A$5:$A$24,0))</f>
+        <v>-19.043659043659</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>2011</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>U열(전년 대비 변화율)에서 해당 연도 값</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="n"/>
+      <c r="I41" s="12" t="n"/>
+      <c r="J41" s="12" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="A32:D32"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30020,23 +30703,23 @@
           <t>구분</t>
         </is>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="13">
         <f>분석!A5</f>
         <v>2005</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="13">
         <f>B3+5</f>
         <v>2010</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="13">
         <f>C3+5</f>
         <v>2015</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="13">
         <f>D3+5</f>
         <v>2020</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="13">
         <f>INDEX(분석!A5:A24,COUNT(분석!D5:D24))</f>
         <v>2024</v>
       </c>
